--- a/workshop_registration_form_templates/046_scholarship_workshop_feedback_form--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/046_scholarship_workshop_feedback_form--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>workshop_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Form Title</t>
+          <t>Workshop Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>workshop_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Workshop Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>workshop_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Workshop Time</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,63 +814,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>workshop_location</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Workshop Location</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>workshop_attendance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Workshop Attendance</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>workshop_comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Workshop Comments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>workshop_suggestions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Workshop Suggestions</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,90 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1006,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1056,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1124,114 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
